--- a/data/trans_dic/P70D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 21,58</t>
+          <t>3,23; 19,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,92</t>
+          <t>1,68; 9,65</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,73</t>
+          <t>1,01; 5,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,2</t>
+          <t>0,95; 5,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,67</t>
+          <t>1,41; 4,31</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,96</t>
+          <t>1,63; 4,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,15</t>
+          <t>2,42; 5,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,78</t>
+          <t>2,44; 4,9</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,96</t>
+          <t>0,96; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,44</t>
+          <t>4,37; 10,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,37</t>
+          <t>2,25; 6,55</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 12,22</t>
+          <t>6,09; 12,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 13,95</t>
+          <t>7,57; 13,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,69</t>
+          <t>7,29; 11,61</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 28,95</t>
+          <t>3,61; 31,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 30,27</t>
+          <t>5,75; 30,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 24,95</t>
+          <t>6,19; 23,95</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,92</t>
+          <t>2,56; 5,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,39</t>
+          <t>4,49; 7,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,72</t>
+          <t>3,63; 5,6</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3610</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2834; 17528</t>
+          <t>2622; 16193</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2850; 17050</t>
+          <t>2889; 16576</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3553; 19994</t>
+          <t>3522; 20458</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3772; 18337</t>
+          <t>3337; 17867</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10012; 32820</t>
+          <t>9868; 30251</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7650; 22952</t>
+          <t>7534; 23047</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8581; 21591</t>
+          <t>8492; 20558</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19338; 38941</t>
+          <t>19859; 39890</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7832; 44456</t>
+          <t>7197; 43426</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19430; 47380</t>
+          <t>19861; 48889</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27138; 76528</t>
+          <t>27032; 78666</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17840; 36529</t>
+          <t>18194; 36177</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15407; 28844</t>
+          <t>15647; 28578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36188; 59137</t>
+          <t>36840; 58736</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>605; 4906</t>
+          <t>612; 5359</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>977; 5325</t>
+          <t>1011; 5353</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2241; 8617</t>
+          <t>2138; 8270</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49777; 96815</t>
+          <t>50276; 101240</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67339; 108218</t>
+          <t>65658; 105418</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>125685; 196400</t>
+          <t>124570; 192169</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P70D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 19,93</t>
+          <t>3,52; 20,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,65</t>
+          <t>1,77; 9,86</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,86</t>
+          <t>1,19; 5,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,06</t>
+          <t>1,72; 6,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,31</t>
+          <t>1,88; 5,03</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,98</t>
+          <t>1,55; 4,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,85</t>
+          <t>2,26; 5,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,9</t>
+          <t>2,26; 4,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,82</t>
+          <t>3,37; 7,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,77</t>
+          <t>4,65; 8,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,55</t>
+          <t>4,32; 7,01</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,1</t>
+          <t>5,92; 12,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 13,83</t>
+          <t>7,24; 13,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,61</t>
+          <t>7,14; 11,45</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,61; 31,63</t>
+          <t>3,55; 30,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,75; 30,43</t>
+          <t>5,46; 27,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 23,95</t>
+          <t>5,27; 22,84</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,15</t>
+          <t>3,49; 5,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,2</t>
+          <t>4,93; 7,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,6</t>
+          <t>4,35; 5,87</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>9342</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2622; 16193</t>
+          <t>3231; 18710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2889; 16576</t>
+          <t>3481; 19375</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>21838</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3522; 20458</t>
+          <t>4692; 21606</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3337; 17867</t>
+          <t>5498; 20539</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9868; 30251</t>
+          <t>13402; 35881</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27995</t>
+          <t>30047</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7534; 23047</t>
+          <t>8387; 24716</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8492; 20558</t>
+          <t>8992; 23061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19859; 39890</t>
+          <t>21178; 42416</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54811</t>
+          <t>55591</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7197; 43426</t>
+          <t>18349; 39480</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19861; 48889</t>
+          <t>21162; 38832</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27032; 78666</t>
+          <t>43198; 70147</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25745</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>51147</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18194; 36177</t>
+          <t>19422; 39854</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15647; 28578</t>
+          <t>16772; 30720</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36840; 58736</t>
+          <t>39937; 64085</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4792</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>612; 5359</t>
+          <t>680; 5772</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1011; 5353</t>
+          <t>1041; 5231</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2138; 8270</t>
+          <t>2013; 8730</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>172759</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>50276; 101240</t>
+          <t>67463; 104557</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>65658; 105418</t>
+          <t>74678; 108319</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>124570; 192169</t>
+          <t>149857; 202238</t>
         </is>
       </c>
     </row>
